--- a/trabajadores.xlsx
+++ b/trabajadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\datosn\Documents\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A925D4-93C2-4070-A1CD-D61C4E6C1F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2D2069-DF48-4EDD-8354-63499A5CD475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
@@ -1022,9 +1022,7 @@
       <c r="M6" s="20">
         <v>0</v>
       </c>
-      <c r="N6" s="7" t="s">
-        <v>52</v>
-      </c>
+      <c r="N6" s="7"/>
       <c r="O6" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1416,7 +1414,9 @@
       <c r="M14" s="20">
         <v>0</v>
       </c>
-      <c r="N14" s="7"/>
+      <c r="N14" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="O14" s="20">
         <f t="shared" si="2"/>
         <v>0</v>

--- a/trabajadores.xlsx
+++ b/trabajadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\datosn\Documents\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2D2069-DF48-4EDD-8354-63499A5CD475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75222E30-DA2C-434A-91A7-BED814F2FB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>CEDULA</t>
   </si>
@@ -192,9 +192,6 @@
   </si>
   <si>
     <t>DESCUENTOS EF</t>
-  </si>
-  <si>
-    <t>hola</t>
   </si>
 </sst>
 </file>
@@ -1412,14 +1409,12 @@
         <v>0</v>
       </c>
       <c r="M14" s="20">
-        <v>0</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>52</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="N14" s="7"/>
       <c r="O14" s="20">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">

--- a/trabajadores.xlsx
+++ b/trabajadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\datosn\Documents\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75222E30-DA2C-434A-91A7-BED814F2FB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2EFAC0-EEBC-47A8-8FFD-DB3980ECEEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
   <si>
     <t>CEDULA</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>DESCUENTOS EF</t>
+  </si>
+  <si>
+    <t>hola</t>
   </si>
 </sst>
 </file>
@@ -819,7 +822,9 @@
       <c r="M2" s="20">
         <v>0</v>
       </c>
-      <c r="N2" s="7"/>
+      <c r="N2" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="O2" s="20">
         <f>K2-L2-M2</f>
         <v>0</v>
@@ -1409,12 +1414,12 @@
         <v>0</v>
       </c>
       <c r="M14" s="20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N14" s="7"/>
       <c r="O14" s="20">
         <f t="shared" si="2"/>
-        <v>-1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">

--- a/trabajadores.xlsx
+++ b/trabajadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\datosn\Documents\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C89640-0066-4B4A-BFE6-ACE1C81FB1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869AECDD-C43F-4BE9-A3A2-FECBBAA8A5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>

--- a/trabajadores.xlsx
+++ b/trabajadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\datosn\Documents\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{032D2C17-D79E-4433-A29B-28F228088222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD50EEC5-A1C7-4499-A082-3898993A079E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1D5E3F1D-C0EF-4F83-A5E1-9AFFAE728395}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>CEDULA</t>
   </si>
@@ -89,142 +89,100 @@
     <t>ESCOBAR GALINDO OLGA PATRICIA</t>
   </si>
   <si>
-    <t xml:space="preserve">20,000 COMPARTIR + 20 COMPARTIR 1,600,000 VALES </t>
-  </si>
-  <si>
     <t>CASTAÑEDA SANCHEZ MAURICIO</t>
   </si>
   <si>
-    <t>35,300 COOSERPARK+20,000 COMPARTIR+207,117 PRESTAMO+100,000 VALES</t>
-  </si>
-  <si>
-    <t>14,000 (2) CARITAS+33,616 UTILIDADES+20,000 COMPARTIR+24,000 SUGERIDOS+220,384 VALES</t>
-  </si>
-  <si>
     <t>CARDOZO REYES JUAN SEBASTIAN</t>
   </si>
   <si>
-    <t>44,700 COOSERPARK+2 DIAS LCNR+20,000 COMPARTIR+150,000 VALES +3 DIAS LCNR +18,000 SUGERIDOS +14,000 (2) CARITAS+15,223 RESTANTE UTILIDAD+252,265 VALES</t>
-  </si>
-  <si>
-    <t>44,926 UTILIDADES</t>
-  </si>
-  <si>
-    <t>MONTAÑO DIAZ RAUL ANDRES</t>
-  </si>
-  <si>
-    <t>25,100 COOSERPARK+20,000 COMPARTIR+300,000 VALES+3 DIAS INCP+ DESPIDO 25 MAY+400,000 VALES</t>
-  </si>
-  <si>
-    <t>35,000 (5) CARITAS+1 DIA 58,363+6,324 UTILIDADES</t>
-  </si>
-  <si>
     <t>TRIVIÑO MOGOLLON FELIPE</t>
   </si>
   <si>
-    <t>20,000 COMPARTIR+210,312 VALES</t>
-  </si>
-  <si>
-    <t>56,000 (8) CARITAS + 1 DIA 58,363+20,000 COMPARTIR</t>
-  </si>
-  <si>
     <t>CHAPARRO TORRES DANIEL</t>
   </si>
   <si>
-    <t>20,000 COMPARTIR+2 DIAS VACACIONES</t>
-  </si>
-  <si>
-    <t>42,000 (6) CARITAS+11,849 UTILIDADE+32,000 SUGERIDOS+269,700 VALES</t>
-  </si>
-  <si>
     <t>JIMENEZ LOPEZ KAREN LISETH</t>
   </si>
   <si>
-    <t>44,700 COOSERPARK+1 DIA LCR+20,000 COMPARTIR+1 DIA LCR+100,000 VALES+14,000 (2) CARITAS+20,000 COMPARTIR</t>
-  </si>
-  <si>
     <t xml:space="preserve">COLLAZOS VELANDIA JHOAN ESNEYDER </t>
   </si>
   <si>
-    <t>35,300 COOSERPARK+VAC 11 AL 16+20,000 COMPARTIR+34,760 PLAN CELULAR+100,000 VALES+1 DIA VAC</t>
-  </si>
-  <si>
-    <t>56,000 (8) CARITAS+8,792 UTILIDADES+20,000 COMPARTIR+17,000 SUGERIDOS+257,786 VALES</t>
-  </si>
-  <si>
     <t>TRIVIÑO RIOS JOSE JULIAN</t>
   </si>
   <si>
-    <t>1 DIA LCNR+20,000 COMPARTIR+85,000 VALES</t>
-  </si>
-  <si>
-    <t>14,000 (2) CARITAS+17,000 SUGERIDOS</t>
-  </si>
-  <si>
     <t>CAMACHO ABRIL SANDRA MILENA</t>
   </si>
   <si>
-    <t>INCP +7 DIAS INCP+21,000 (3) CARITAS+14,000 SUGERIDOS</t>
-  </si>
-  <si>
     <t>ALVAREZ ESCOBAR JUAN ESTEBAN</t>
   </si>
   <si>
-    <t>DIAS DE VACACIONES</t>
-  </si>
-  <si>
     <t>DURAN BURGOS PEDRO SIDEL</t>
   </si>
   <si>
     <t>PINZON VILLARREAL LADY VANESSA</t>
   </si>
   <si>
-    <t>20,000 COMPARTIR+378,474 PRESTAMOS+42,000 (6) CARITAS+20000 COMPARTIR</t>
-  </si>
-  <si>
     <t>ALVAREZ ESCOBAR NICOLAS ENRIQUE</t>
   </si>
   <si>
-    <t>20,000 COMPARTIR +20,000 COMPARTIR</t>
-  </si>
-  <si>
     <t>RAMIREZ VARGAS SANTIAGO ANDRES</t>
   </si>
   <si>
-    <t>INCP+20,000 COMPARTIR+5 DIAS INCP+21,000 (3) CARITAS+20,000 COMPARTIR+158,300 VALES</t>
-  </si>
-  <si>
     <t>SUAREZ ORTIZ DANNY ALEJANDRO</t>
   </si>
   <si>
-    <t>20,000 COMPARTIR+49,000 (7) CARITAS</t>
-  </si>
-  <si>
-    <t>MONTOYA DIAZ ENOC ALEXANDER</t>
-  </si>
-  <si>
-    <t>20,000 COMPARTIR+150,000 PRESTAMO</t>
-  </si>
-  <si>
     <t>HERNANDEZ MONTAÑO DAVID ALEXANDER</t>
   </si>
   <si>
-    <t>20,000 COMPARTIR+200,000 VALES+7,000 (1) CARITA+265,748 VALES</t>
-  </si>
-  <si>
     <t>TOVAR AREVALO JULIAN GIOVANNI</t>
   </si>
   <si>
     <t>HERRERA NINCO JUAN SEBASTIAN</t>
   </si>
   <si>
-    <t>ING 4 MAYO+20,000 COMPARTIR+20,000 COMPARTIR+20,000 VALE PERSONAL</t>
-  </si>
-  <si>
     <t>DIONISIO NAVARRETE JOHAN ANDREY</t>
   </si>
   <si>
-    <t>ING 13 MAYO +20,000 COMPARTIR+42,000 (6) CARITAS+20,000 COMPARTIR+88,000 VALES</t>
+    <t>35,300 COOSERPARK+5,000 COMPARTIR+109,424 VALES</t>
+  </si>
+  <si>
+    <t>44,700 COOSERPARK+25,000 COMPARTIR+203,466 VALES</t>
+  </si>
+  <si>
+    <t>5,000 COMPARTIR+169,418 VALES</t>
+  </si>
+  <si>
+    <t>25,000 COMPARTIR+25,000 JUEGO LADY ESPOSA+8203 VALES</t>
+  </si>
+  <si>
+    <t>44,700 COOSERPARK+5,000 COMPARTIR+100,000 VALES+9922 DOMINICAL</t>
+  </si>
+  <si>
+    <t>35,3000 COOSPERPARK+5,000 COMPARITIR+34,760 PLAN CELULAR +158,115 VALES</t>
+  </si>
+  <si>
+    <t>3 DIAS VACIONES + 1 DIA LCNR</t>
+  </si>
+  <si>
+    <t>372,354 PRESTAMO+5,000 COMPARTIR</t>
+  </si>
+  <si>
+    <t>5,000 COMPARTIR</t>
+  </si>
+  <si>
+    <t>5,000 COMPARTIR+158,300 VALES</t>
+  </si>
+  <si>
+    <t>25,000 COMPARTIR</t>
+  </si>
+  <si>
+    <t>25,000 COMPARTIR+185,000 VALES</t>
+  </si>
+  <si>
+    <t>80,000 VALES</t>
+  </si>
+  <si>
+    <t>5,000 COMPARTIR+2 DIAS LCR +150,000 VALE</t>
   </si>
 </sst>
 </file>
@@ -237,7 +195,7 @@
     <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,6 +234,13 @@
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -285,7 +250,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -321,6 +286,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -329,7 +305,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -369,6 +345,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -708,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29A9C67D-0A08-4F51-94EF-1187BF4EB1B2}">
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="13" bestFit="1" customWidth="1"/>
@@ -790,28 +781,29 @@
         <v>16</v>
       </c>
       <c r="C2" s="8">
-        <v>8000000.0000000009</v>
+        <f>8000000/30*15</f>
+        <v>4000000.0000000005</v>
       </c>
       <c r="D2" s="9">
+        <f>200000/30*0</f>
         <v>0</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>640000.00000000012</v>
+        <v>0</v>
       </c>
       <c r="G2" s="10">
         <v>0</v>
       </c>
       <c r="H2" s="10">
-        <v>1640000</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>17</v>
-      </c>
+        <v>700000</v>
+      </c>
+      <c r="I2" s="14"/>
       <c r="J2" s="10">
-        <v>5720000.0000000009</v>
+        <f>+C2+D2+E2-F2+G2-H2</f>
+        <v>3300000.0000000005</v>
       </c>
       <c r="K2" s="10">
         <v>0</v>
@@ -831,288 +823,302 @@
       </c>
       <c r="Q2" s="5"/>
     </row>
-    <row r="3" spans="1:18" ht="27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>94288721</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="8">
-        <v>1750905</v>
-      </c>
-      <c r="D3" s="9">
-        <v>249094.99999999997</v>
+        <v>17</v>
+      </c>
+      <c r="C3" s="15">
+        <f>1750905/30*15</f>
+        <v>875452.5</v>
+      </c>
+      <c r="D3" s="16">
+        <f>249095/30*15</f>
+        <v>124547.49999999999</v>
       </c>
       <c r="E3" s="10">
         <v>0</v>
       </c>
       <c r="F3" s="10">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G3" s="10">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="H3" s="10">
-        <v>362417</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>19</v>
+        <f>114424+35300</f>
+        <v>149724</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>35</v>
       </c>
       <c r="J3" s="10">
-        <v>2197510.6</v>
+        <f t="shared" ref="J3:J19" si="0">+C3+D3+E3-F3+G3-H3</f>
+        <v>850276</v>
       </c>
       <c r="K3" s="10">
-        <v>1505035</v>
+        <v>0</v>
       </c>
       <c r="L3" s="10">
-        <v>805000</v>
+        <v>0</v>
       </c>
       <c r="M3" s="10">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="N3" s="12">
-        <v>298000</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>20</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O3" s="11"/>
       <c r="P3" s="12">
-        <v>493000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="40.5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>1001200622</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="8">
-        <v>1459087.5</v>
-      </c>
-      <c r="D4" s="9">
-        <v>207579.16666666666</v>
+        <v>18</v>
+      </c>
+      <c r="C4" s="15">
+        <f>1750905/30*15</f>
+        <v>875452.5</v>
+      </c>
+      <c r="D4" s="16">
+        <f>249095/30*15</f>
+        <v>124547.49999999999</v>
       </c>
       <c r="E4" s="10">
         <v>0</v>
       </c>
       <c r="F4" s="10">
-        <v>116727</v>
+        <v>0</v>
       </c>
       <c r="G4" s="10">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="H4" s="10">
-        <v>514188</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>22</v>
+        <f>228466+44700</f>
+        <v>273166</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>36</v>
       </c>
       <c r="J4" s="10">
-        <v>1635751.666666667</v>
+        <f t="shared" si="0"/>
+        <v>726834</v>
       </c>
       <c r="K4" s="10">
-        <v>644926</v>
+        <v>0</v>
       </c>
       <c r="L4" s="10">
-        <v>44926</v>
+        <v>0</v>
       </c>
       <c r="M4" s="10">
         <v>0</v>
       </c>
       <c r="N4" s="12">
-        <v>44926</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>23</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O4" s="11"/>
       <c r="P4" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>1000362431</v>
+        <v>1001045472</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="8">
-        <v>1459087.5</v>
-      </c>
-      <c r="D5" s="9">
-        <v>182669.66666666666</v>
+        <v>19</v>
+      </c>
+      <c r="C5" s="15">
+        <f>1750905/30*15</f>
+        <v>875452.5</v>
+      </c>
+      <c r="D5" s="16">
+        <f>249095/30*15</f>
+        <v>124547.49999999999</v>
       </c>
       <c r="E5" s="10">
         <v>0</v>
       </c>
       <c r="F5" s="10">
-        <v>116727</v>
+        <v>0</v>
       </c>
       <c r="G5" s="10">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="H5" s="10">
-        <v>745100</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>25</v>
+        <v>174418</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>37</v>
       </c>
       <c r="J5" s="10">
-        <v>1179930.1666666667</v>
+        <f t="shared" si="0"/>
+        <v>825582</v>
       </c>
       <c r="K5" s="10">
-        <v>531685</v>
+        <v>0</v>
       </c>
       <c r="L5" s="10">
-        <v>131685</v>
+        <v>0</v>
       </c>
       <c r="M5" s="10">
-        <v>93363</v>
+        <v>0</v>
       </c>
       <c r="N5" s="12">
-        <v>6324</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>26</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O5" s="11"/>
       <c r="P5" s="12">
-        <v>31998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>1001045472</v>
+        <v>80875830</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="8">
-        <v>1750905</v>
-      </c>
-      <c r="D6" s="9">
-        <v>249094.99999999997</v>
+        <v>20</v>
+      </c>
+      <c r="C6" s="15">
+        <f>1750905/30*14</f>
+        <v>817089</v>
+      </c>
+      <c r="D6" s="16">
+        <f>249095/30*14</f>
+        <v>116244.33333333333</v>
       </c>
       <c r="E6" s="10">
         <v>0</v>
       </c>
       <c r="F6" s="10">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G6" s="10">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="H6" s="10">
-        <v>230312</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>28</v>
+        <v>58203</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>38</v>
       </c>
       <c r="J6" s="10">
-        <v>2329615.6</v>
+        <f t="shared" si="0"/>
+        <v>875130.33333333337</v>
       </c>
       <c r="K6" s="10">
-        <v>1230108</v>
+        <v>0</v>
       </c>
       <c r="L6" s="10">
-        <v>530108</v>
+        <v>0</v>
       </c>
       <c r="M6" s="10">
-        <v>114363</v>
+        <v>0</v>
       </c>
       <c r="N6" s="12">
-        <v>20000</v>
-      </c>
-      <c r="O6" s="11" t="s">
-        <v>29</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O6" s="11"/>
       <c r="P6" s="12">
-        <v>395745</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="27" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>80875830</v>
+        <v>1006116706</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="8">
-        <v>1634178</v>
-      </c>
-      <c r="D7" s="9">
-        <v>232488.66666666666</v>
+        <v>21</v>
+      </c>
+      <c r="C7" s="15">
+        <f>1750905/30*14</f>
+        <v>817089</v>
+      </c>
+      <c r="D7" s="16">
+        <f>249095/30*13</f>
+        <v>107941.16666666666</v>
       </c>
       <c r="E7" s="10">
         <v>0</v>
       </c>
       <c r="F7" s="10">
-        <v>130734.24</v>
+        <v>0</v>
       </c>
       <c r="G7" s="10">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="H7" s="10">
-        <v>20000</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>31</v>
+        <f>114922+44700</f>
+        <v>159622</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="J7" s="10">
-        <v>2415932.4266666668</v>
+        <f t="shared" si="0"/>
+        <v>765408.16666666663</v>
       </c>
       <c r="K7" s="10">
-        <v>1207249</v>
+        <v>0</v>
       </c>
       <c r="L7" s="10">
-        <v>507249</v>
+        <v>0</v>
       </c>
       <c r="M7" s="10">
-        <v>42000</v>
+        <v>0</v>
       </c>
       <c r="N7" s="12">
-        <v>313549</v>
-      </c>
-      <c r="O7" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O7" s="11"/>
       <c r="P7" s="12">
-        <v>151700</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="27" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>1006116706</v>
+        <v>1193092448</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="8">
-        <v>1750905</v>
-      </c>
-      <c r="D8" s="9">
-        <v>232488.66666666666</v>
+        <v>22</v>
+      </c>
+      <c r="C8" s="15">
+        <f>1750905/30*15</f>
+        <v>875452.5</v>
+      </c>
+      <c r="D8" s="16">
+        <f>249095/30*15</f>
+        <v>124547.49999999999</v>
       </c>
       <c r="E8" s="10">
         <v>0</v>
       </c>
       <c r="F8" s="10">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G8" s="10">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="H8" s="10">
-        <v>198700</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>34</v>
+        <f>197875+35300</f>
+        <v>233175</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>40</v>
       </c>
       <c r="J8" s="10">
-        <v>1744621.2666666668</v>
-      </c>
-      <c r="K8" s="10"/>
+        <f t="shared" si="0"/>
+        <v>766825</v>
+      </c>
+      <c r="K8" s="10">
+        <v>0</v>
+      </c>
       <c r="L8" s="10">
         <v>0</v>
       </c>
@@ -1127,136 +1133,137 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>1193092448</v>
+        <v>79910037</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="8">
-        <v>1400724</v>
-      </c>
-      <c r="D9" s="9">
-        <v>199276</v>
+        <v>23</v>
+      </c>
+      <c r="C9" s="15">
+        <f>1750905/30*15</f>
+        <v>875452.5</v>
+      </c>
+      <c r="D9" s="16">
+        <f>249095/30*15</f>
+        <v>124547.49999999999</v>
       </c>
       <c r="E9" s="10">
         <v>0</v>
       </c>
       <c r="F9" s="10">
-        <v>112057.92</v>
+        <v>0</v>
       </c>
       <c r="G9" s="10">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="H9" s="10">
-        <v>476606.66666666663</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>36</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I9" s="14"/>
       <c r="J9" s="10">
-        <v>1711335.4133333336</v>
+        <f t="shared" si="0"/>
+        <v>1000000</v>
       </c>
       <c r="K9" s="10">
-        <v>1227182</v>
+        <v>0</v>
       </c>
       <c r="L9" s="10">
-        <v>527182</v>
+        <v>0</v>
       </c>
       <c r="M9" s="10">
-        <v>56000</v>
+        <v>0</v>
       </c>
       <c r="N9" s="12">
-        <v>303668</v>
-      </c>
-      <c r="O9" s="11" t="s">
-        <v>37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O9" s="11"/>
       <c r="P9" s="12">
-        <v>167514</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>79910037</v>
+        <v>52767162</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="8">
-        <v>1750905</v>
-      </c>
-      <c r="D10" s="9">
-        <v>249094.99999999997</v>
+        <v>24</v>
+      </c>
+      <c r="C10" s="15">
+        <f>1750905/30*11</f>
+        <v>641998.5</v>
+      </c>
+      <c r="D10" s="16">
+        <f>249095/30*11</f>
+        <v>91334.833333333328</v>
       </c>
       <c r="E10" s="10">
-        <v>0</v>
+        <v>23877</v>
       </c>
       <c r="F10" s="10">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G10" s="10">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="H10" s="10">
-        <v>105000</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>39</v>
+        <v>0</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="J10" s="10">
-        <v>2054927.6</v>
+        <f t="shared" si="0"/>
+        <v>757210.33333333337</v>
       </c>
       <c r="K10" s="10">
-        <v>474632</v>
+        <v>0</v>
       </c>
       <c r="L10" s="10">
-        <v>174632</v>
+        <v>0</v>
       </c>
       <c r="M10" s="10">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="N10" s="12">
-        <v>17000</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>40</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O10" s="11"/>
       <c r="P10" s="12">
-        <v>143632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>52767162</v>
+        <v>1000795016</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="8">
-        <v>875452.5</v>
-      </c>
-      <c r="D11" s="9">
-        <v>83031.666666666657</v>
+        <v>25</v>
+      </c>
+      <c r="C11" s="15">
+        <f>+(2150000/30)*15</f>
+        <v>1075000</v>
+      </c>
+      <c r="D11" s="16">
+        <f>249095/30*15</f>
+        <v>124547.49999999999</v>
       </c>
       <c r="E11" s="10">
         <v>0</v>
       </c>
       <c r="F11" s="10">
-        <v>70036.2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="10">
         <v>0</v>
       </c>
       <c r="H11" s="10">
-        <v>35000</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>42</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" s="14"/>
       <c r="J11" s="10">
-        <v>853447.96666666667</v>
+        <f t="shared" si="0"/>
+        <v>1199547.5</v>
       </c>
       <c r="K11" s="10">
         <v>0</v>
@@ -1277,38 +1284,39 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>1000795016</v>
+        <v>79593400</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="8">
-        <v>1666666.6666666667</v>
-      </c>
-      <c r="D12" s="9">
-        <v>207579.16666666666</v>
+        <v>26</v>
+      </c>
+      <c r="C12" s="15">
+        <v>7150000</v>
+      </c>
+      <c r="D12" s="16">
+        <v>0</v>
       </c>
       <c r="E12" s="10">
         <v>0</v>
       </c>
       <c r="F12" s="10">
-        <v>133333.33333333334</v>
+        <v>0</v>
       </c>
       <c r="G12" s="10">
-        <v>90373</v>
+        <v>0</v>
       </c>
       <c r="H12" s="10">
-        <v>249095</v>
-      </c>
-      <c r="I12" s="11"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="14"/>
       <c r="J12" s="10">
-        <v>1582190.5000000002</v>
+        <f t="shared" si="0"/>
+        <v>7150000</v>
       </c>
       <c r="K12" s="10">
         <v>0</v>
       </c>
       <c r="L12" s="10">
-        <v>259000</v>
+        <v>0</v>
       </c>
       <c r="M12" s="10">
         <v>0</v>
@@ -1316,47 +1324,50 @@
       <c r="N12" s="12">
         <v>0</v>
       </c>
-      <c r="O12" s="11" t="s">
-        <v>44</v>
-      </c>
+      <c r="O12" s="11"/>
       <c r="P12" s="12">
-        <v>259000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>79593400</v>
+        <v>1023029896</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="8">
-        <v>7150000</v>
-      </c>
-      <c r="D13" s="9">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="C13" s="15">
+        <f>1750905/30*15</f>
+        <v>875452.5</v>
+      </c>
+      <c r="D13" s="16">
+        <f t="shared" ref="D13:D18" si="1">249095/30*15</f>
+        <v>124547.49999999999</v>
       </c>
       <c r="E13" s="10">
         <v>0</v>
       </c>
       <c r="F13" s="10">
-        <v>572000</v>
+        <v>0</v>
       </c>
       <c r="G13" s="10">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="H13" s="10">
-        <v>0</v>
-      </c>
-      <c r="I13" s="11"/>
+        <v>377354</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>42</v>
+      </c>
       <c r="J13" s="10">
-        <v>8578000</v>
+        <f t="shared" si="0"/>
+        <v>622646</v>
       </c>
       <c r="K13" s="10">
         <v>0</v>
       </c>
       <c r="L13" s="10">
-        <v>572000</v>
+        <v>0</v>
       </c>
       <c r="M13" s="10">
         <v>0</v>
@@ -1366,39 +1377,42 @@
       </c>
       <c r="O13" s="11"/>
       <c r="P13" s="12">
-        <v>572000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="27" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>1023029896</v>
+        <v>1015473856</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="8">
-        <v>1750905</v>
-      </c>
-      <c r="D14" s="9">
-        <v>249094.99999999997</v>
+        <v>28</v>
+      </c>
+      <c r="C14" s="15">
+        <f>+((2200000/30)*15)</f>
+        <v>1100000</v>
+      </c>
+      <c r="D14" s="16">
+        <f t="shared" si="1"/>
+        <v>124547.49999999999</v>
       </c>
       <c r="E14" s="10">
         <v>0</v>
       </c>
       <c r="F14" s="10">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G14" s="10">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="H14" s="10">
-        <v>460474</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>47</v>
+        <v>5000</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="J14" s="10">
-        <v>1499453.6</v>
+        <f t="shared" si="0"/>
+        <v>1219547.5</v>
       </c>
       <c r="K14" s="10">
         <v>0</v>
@@ -1419,34 +1433,37 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>1015473856</v>
+        <v>1026306646</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="8">
-        <v>2200000</v>
-      </c>
-      <c r="D15" s="9">
-        <v>249094.99999999997</v>
+        <v>29</v>
+      </c>
+      <c r="C15" s="15">
+        <f t="shared" ref="C15:C20" si="2">1750905/30*15</f>
+        <v>875452.5</v>
+      </c>
+      <c r="D15" s="16">
+        <f t="shared" si="1"/>
+        <v>124547.49999999999</v>
       </c>
       <c r="E15" s="10">
         <v>0</v>
       </c>
       <c r="F15" s="10">
-        <v>176000</v>
+        <v>0</v>
       </c>
       <c r="G15" s="10">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="H15" s="10">
-        <v>40000</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>49</v>
+        <v>163300</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="J15" s="10">
-        <v>2833095</v>
+        <f t="shared" si="0"/>
+        <v>836700</v>
       </c>
       <c r="K15" s="10">
         <v>0</v>
@@ -1465,36 +1482,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>1026306646</v>
+        <v>1003533086</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="8">
-        <v>1750905</v>
-      </c>
-      <c r="D16" s="9">
-        <v>83031.666666666657</v>
+        <v>30</v>
+      </c>
+      <c r="C16" s="15">
+        <f t="shared" si="2"/>
+        <v>875452.5</v>
+      </c>
+      <c r="D16" s="16">
+        <f t="shared" si="1"/>
+        <v>124547.49999999999</v>
       </c>
       <c r="E16" s="10">
-        <v>6036</v>
+        <v>0</v>
       </c>
       <c r="F16" s="10">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G16" s="10">
         <v>0</v>
       </c>
       <c r="H16" s="10">
-        <v>219300</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>51</v>
+        <v>25000</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>45</v>
       </c>
       <c r="J16" s="10">
-        <v>1480600.2666666668</v>
+        <f t="shared" si="0"/>
+        <v>975000</v>
       </c>
       <c r="K16" s="10">
         <v>0</v>
@@ -1513,36 +1533,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>1003533086</v>
+        <v>1028660836</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="8">
-        <v>1750905</v>
-      </c>
-      <c r="D17" s="9">
-        <v>249094.99999999997</v>
+        <v>31</v>
+      </c>
+      <c r="C17" s="15">
+        <f t="shared" si="2"/>
+        <v>875452.5</v>
+      </c>
+      <c r="D17" s="16">
+        <f t="shared" si="1"/>
+        <v>124547.49999999999</v>
       </c>
       <c r="E17" s="10">
-        <v>320477</v>
+        <v>0</v>
       </c>
       <c r="F17" s="10">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G17" s="10">
         <v>0</v>
       </c>
       <c r="H17" s="10">
-        <v>69000</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>53</v>
+        <v>210000</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>46</v>
       </c>
       <c r="J17" s="10">
-        <v>2111404.6</v>
+        <f t="shared" si="0"/>
+        <v>790000</v>
       </c>
       <c r="K17" s="10">
         <v>0</v>
@@ -1563,34 +1586,37 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>1000808758</v>
+        <v>1123436140</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="8">
-        <v>1750905</v>
-      </c>
-      <c r="D18" s="9">
-        <v>249094.99999999997</v>
+        <v>32</v>
+      </c>
+      <c r="C18" s="15">
+        <f t="shared" si="2"/>
+        <v>875452.5</v>
+      </c>
+      <c r="D18" s="16">
+        <f t="shared" si="1"/>
+        <v>124547.49999999999</v>
       </c>
       <c r="E18" s="10">
         <v>0</v>
       </c>
       <c r="F18" s="10">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G18" s="10">
         <v>0</v>
       </c>
       <c r="H18" s="10">
-        <v>170000</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>55</v>
+        <v>80000</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>47</v>
       </c>
       <c r="J18" s="10">
-        <v>1689927.6</v>
+        <f t="shared" si="0"/>
+        <v>920000</v>
       </c>
       <c r="K18" s="10">
         <v>0</v>
@@ -1609,36 +1635,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>1028660836</v>
+        <v>1003950486</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="8">
-        <v>1750905</v>
-      </c>
-      <c r="D19" s="9">
-        <v>249094.99999999997</v>
+        <v>33</v>
+      </c>
+      <c r="C19" s="15">
+        <f t="shared" si="2"/>
+        <v>875452.5</v>
+      </c>
+      <c r="D19" s="16">
+        <f>249095/30*14</f>
+        <v>116244.33333333333</v>
       </c>
       <c r="E19" s="10">
-        <v>380143</v>
+        <v>0</v>
       </c>
       <c r="F19" s="10">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G19" s="10">
         <v>0</v>
       </c>
       <c r="H19" s="10">
-        <v>492748</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>57</v>
+        <v>155000</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>48</v>
       </c>
       <c r="J19" s="10">
-        <v>1747322.6</v>
+        <f t="shared" si="0"/>
+        <v>836696.83333333337</v>
       </c>
       <c r="K19" s="10">
         <v>0</v>
@@ -1659,22 +1688,24 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>1123436140</v>
+        <v>1053330769</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="8">
-        <v>1750905</v>
-      </c>
-      <c r="D20" s="9">
-        <v>249094.99999999997</v>
+        <v>34</v>
+      </c>
+      <c r="C20" s="15">
+        <f t="shared" si="2"/>
+        <v>875452.5</v>
+      </c>
+      <c r="D20" s="16">
+        <f>249095/30*15</f>
+        <v>124547.49999999999</v>
       </c>
       <c r="E20" s="10">
         <v>0</v>
       </c>
       <c r="F20" s="10">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G20" s="10">
         <v>0</v>
@@ -1682,9 +1713,10 @@
       <c r="H20" s="10">
         <v>0</v>
       </c>
-      <c r="I20" s="11"/>
+      <c r="I20" s="17"/>
       <c r="J20" s="10">
-        <v>1859927.6</v>
+        <f>+C20+D20+E20-F20+G20-H20</f>
+        <v>1000000</v>
       </c>
       <c r="K20" s="10">
         <v>0</v>
@@ -1704,36 +1736,16 @@
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
-        <v>1003950486</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="8">
-        <v>1400724</v>
-      </c>
-      <c r="D21" s="9">
-        <v>224185.49999999997</v>
-      </c>
-      <c r="E21" s="10">
-        <v>539879</v>
-      </c>
-      <c r="F21" s="10">
-        <v>112057.92</v>
-      </c>
-      <c r="G21" s="10">
-        <v>0</v>
-      </c>
-      <c r="H21" s="10">
-        <v>60000</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="J21" s="10">
-        <v>1992730.58</v>
-      </c>
+      <c r="A21" s="6"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="10"/>
       <c r="K21" s="10">
         <v>0</v>
       </c>
@@ -1748,54 +1760,6 @@
       </c>
       <c r="O21" s="11"/>
       <c r="P21" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="27" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
-        <v>1053330769</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="8">
-        <v>1050543</v>
-      </c>
-      <c r="D22" s="9">
-        <v>149457</v>
-      </c>
-      <c r="E22" s="10">
-        <v>255438</v>
-      </c>
-      <c r="F22" s="10">
-        <v>84043.44</v>
-      </c>
-      <c r="G22" s="10">
-        <v>0</v>
-      </c>
-      <c r="H22" s="10">
-        <v>170000</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="J22" s="10">
-        <v>1201394.56</v>
-      </c>
-      <c r="K22" s="10">
-        <v>0</v>
-      </c>
-      <c r="L22" s="10">
-        <v>0</v>
-      </c>
-      <c r="M22" s="10">
-        <v>0</v>
-      </c>
-      <c r="N22" s="12">
-        <v>0</v>
-      </c>
-      <c r="O22" s="11"/>
-      <c r="P22" s="12">
         <v>0</v>
       </c>
     </row>

--- a/trabajadores.xlsx
+++ b/trabajadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\datosn\Documents\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD50EEC5-A1C7-4499-A082-3898993A079E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C6AB59B-D89E-4A90-817F-D53F425BB28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1D5E3F1D-C0EF-4F83-A5E1-9AFFAE728395}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>CEDULA</t>
   </si>
@@ -143,46 +143,73 @@
     <t>DIONISIO NAVARRETE JOHAN ANDREY</t>
   </si>
   <si>
-    <t>35,300 COOSERPARK+5,000 COMPARTIR+109,424 VALES</t>
-  </si>
-  <si>
-    <t>44,700 COOSERPARK+25,000 COMPARTIR+203,466 VALES</t>
-  </si>
-  <si>
-    <t>5,000 COMPARTIR+169,418 VALES</t>
-  </si>
-  <si>
-    <t>25,000 COMPARTIR+25,000 JUEGO LADY ESPOSA+8203 VALES</t>
-  </si>
-  <si>
-    <t>44,700 COOSERPARK+5,000 COMPARTIR+100,000 VALES+9922 DOMINICAL</t>
-  </si>
-  <si>
-    <t>35,3000 COOSPERPARK+5,000 COMPARITIR+34,760 PLAN CELULAR +158,115 VALES</t>
-  </si>
-  <si>
-    <t>3 DIAS VACIONES + 1 DIA LCNR</t>
-  </si>
-  <si>
-    <t>372,354 PRESTAMO+5,000 COMPARTIR</t>
-  </si>
-  <si>
-    <t>5,000 COMPARTIR</t>
-  </si>
-  <si>
-    <t>5,000 COMPARTIR+158,300 VALES</t>
-  </si>
-  <si>
-    <t>25,000 COMPARTIR</t>
-  </si>
-  <si>
-    <t>25,000 COMPARTIR+185,000 VALES</t>
-  </si>
-  <si>
-    <t>80,000 VALES</t>
-  </si>
-  <si>
-    <t>5,000 COMPARTIR+2 DIAS LCR +150,000 VALE</t>
+    <t>1,000,000 VALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213,889 VALES </t>
+  </si>
+  <si>
+    <t>18,583 UTILIDADES + 18,000 SUGERIDOS + 21,000 CARITAS</t>
+  </si>
+  <si>
+    <t>450,000 VALES</t>
+  </si>
+  <si>
+    <t>35,938 UTILIDADES + 12,000 SUGERIDOS + 35,000 CARITAS</t>
+  </si>
+  <si>
+    <t>300,000 VALES</t>
+  </si>
+  <si>
+    <t>151,726 CARITAS</t>
+  </si>
+  <si>
+    <t>392,854 VALES</t>
+  </si>
+  <si>
+    <t>54,059 UTILIDADES + 20,000 SUGERIDOS + 49,000 CARITAS</t>
+  </si>
+  <si>
+    <t>1 DIA VAC+7,000 CARITAS+57,822 VALES</t>
+  </si>
+  <si>
+    <t>210,089 CARITAS + 5,042 UTILIDADES + 16,000 SUGERIDOS+57,257 COMISION + 200,000 VALES</t>
+  </si>
+  <si>
+    <t>16,000 SUGERIDOS</t>
+  </si>
+  <si>
+    <t>14,000 CARITAS</t>
+  </si>
+  <si>
+    <t>1 DIA LCR + 36,000 SUGERIDOS + 7,000 CARITAS+ 15,000 VALE</t>
+  </si>
+  <si>
+    <t>1 DIA LNCR + 7,000 CARITAS</t>
+  </si>
+  <si>
+    <t>35,000 CARITAS</t>
+  </si>
+  <si>
+    <t>28,000 CARITAS</t>
+  </si>
+  <si>
+    <t>1 DIA LCNR+9,992 DOMINICAL+281,155 VALES</t>
+  </si>
+  <si>
+    <t>1 DIA LCNR+9,992 DOMINICAL + 28,000 CARITAS+75,000 VALES</t>
+  </si>
+  <si>
+    <t>1 DIA LCR +1 DIA LCNR + PAGO EL 1/07/2026</t>
+  </si>
+  <si>
+    <t>151,726 CARITAS + 1 DIA LCL</t>
+  </si>
+  <si>
+    <t>BRYAN ALEJANDRO SANCHEZ GARCIA</t>
+  </si>
+  <si>
+    <t>INGRESA 23 JUN+150,000 VALES</t>
   </si>
 </sst>
 </file>
@@ -236,21 +263,27 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -286,17 +319,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -305,7 +327,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -346,20 +368,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -699,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29A9C67D-0A08-4F51-94EF-1187BF4EB1B2}">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="13" bestFit="1" customWidth="1"/>
@@ -781,29 +815,29 @@
         <v>16</v>
       </c>
       <c r="C2" s="8">
-        <f>8000000/30*15</f>
         <v>4000000.0000000005</v>
       </c>
       <c r="D2" s="9">
-        <f>200000/30*0</f>
         <v>0</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>0</v>
+        <v>640000.00000000012</v>
       </c>
       <c r="G2" s="10">
         <v>0</v>
       </c>
       <c r="H2" s="10">
-        <v>700000</v>
-      </c>
-      <c r="I2" s="14"/>
+        <v>1000000</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>35</v>
+      </c>
       <c r="J2" s="10">
         <f>+C2+D2+E2-F2+G2-H2</f>
-        <v>3300000.0000000005</v>
+        <v>2360000.0000000005</v>
       </c>
       <c r="K2" s="10">
         <v>0</v>
@@ -817,8 +851,9 @@
       <c r="N2" s="12">
         <v>0</v>
       </c>
-      <c r="O2" s="11"/>
+      <c r="O2" s="17"/>
       <c r="P2" s="12">
+        <f>L2-M2-N2</f>
         <v>0</v>
       </c>
       <c r="Q2" s="5"/>
@@ -830,49 +865,49 @@
       <c r="B3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="15">
-        <f>1750905/30*15</f>
+      <c r="C3" s="14">
         <v>875452.5</v>
       </c>
-      <c r="D3" s="16">
-        <f>249095/30*15</f>
+      <c r="D3" s="15">
         <v>124547.49999999999</v>
       </c>
       <c r="E3" s="10">
         <v>0</v>
       </c>
       <c r="F3" s="10">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G3" s="10">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="H3" s="10">
-        <f>114424+35300</f>
-        <v>149724</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>35</v>
+        <v>213889</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>36</v>
       </c>
       <c r="J3" s="10">
         <f t="shared" ref="J3:J19" si="0">+C3+D3+E3-F3+G3-H3</f>
-        <v>850276</v>
+        <v>1346038.6</v>
       </c>
       <c r="K3" s="10">
-        <v>0</v>
+        <v>1702390</v>
       </c>
       <c r="L3" s="10">
-        <v>0</v>
+        <v>1002390</v>
       </c>
       <c r="M3" s="10">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="N3" s="12">
-        <v>0</v>
-      </c>
-      <c r="O3" s="11"/>
+        <v>36583</v>
+      </c>
+      <c r="O3" s="17" t="s">
+        <v>37</v>
+      </c>
       <c r="P3" s="12">
-        <v>0</v>
+        <f>L3-M3-N3</f>
+        <v>944807</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -882,49 +917,49 @@
       <c r="B4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="15">
-        <f>1750905/30*15</f>
+      <c r="C4" s="14">
         <v>875452.5</v>
       </c>
-      <c r="D4" s="16">
-        <f>249095/30*15</f>
+      <c r="D4" s="15">
         <v>124547.49999999999</v>
       </c>
       <c r="E4" s="10">
         <v>0</v>
       </c>
       <c r="F4" s="10">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G4" s="10">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="H4" s="10">
-        <f>228466+44700</f>
-        <v>273166</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>36</v>
+        <v>450000</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>38</v>
       </c>
       <c r="J4" s="10">
         <f t="shared" si="0"/>
-        <v>726834</v>
+        <v>1009927.6000000001</v>
       </c>
       <c r="K4" s="10">
-        <v>0</v>
+        <v>1231400</v>
       </c>
       <c r="L4" s="10">
-        <v>0</v>
+        <v>631400</v>
       </c>
       <c r="M4" s="10">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="N4" s="12">
-        <v>0</v>
-      </c>
-      <c r="O4" s="11"/>
+        <v>47938</v>
+      </c>
+      <c r="O4" s="19" t="s">
+        <v>39</v>
+      </c>
       <c r="P4" s="12">
-        <v>0</v>
+        <f t="shared" ref="P4:P20" si="1">L4-M4-N4</f>
+        <v>548462</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -934,48 +969,49 @@
       <c r="B5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="15">
-        <f>1750905/30*15</f>
+      <c r="C5" s="14">
         <v>875452.5</v>
       </c>
-      <c r="D5" s="16">
-        <f>249095/30*15</f>
+      <c r="D5" s="15">
         <v>124547.49999999999</v>
       </c>
       <c r="E5" s="10">
         <v>0</v>
       </c>
       <c r="F5" s="10">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G5" s="10">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="H5" s="10">
-        <v>174418</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>37</v>
+        <v>300000</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>40</v>
       </c>
       <c r="J5" s="10">
         <f t="shared" si="0"/>
-        <v>825582</v>
+        <v>1259927.6000000001</v>
       </c>
       <c r="K5" s="10">
-        <v>0</v>
+        <v>1290748</v>
       </c>
       <c r="L5" s="10">
-        <v>0</v>
+        <v>590748</v>
       </c>
       <c r="M5" s="10">
-        <v>0</v>
+        <v>151726</v>
       </c>
       <c r="N5" s="12">
         <v>0</v>
       </c>
-      <c r="O5" s="11"/>
+      <c r="O5" s="17" t="s">
+        <v>41</v>
+      </c>
       <c r="P5" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>439022</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -985,84 +1021,82 @@
       <c r="B6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="15">
-        <f>1750905/30*14</f>
-        <v>817089</v>
-      </c>
-      <c r="D6" s="16">
-        <f>249095/30*14</f>
-        <v>116244.33333333333</v>
+      <c r="C6" s="14">
+        <v>875452.5</v>
+      </c>
+      <c r="D6" s="15">
+        <v>124547.49999999999</v>
       </c>
       <c r="E6" s="10">
         <v>0</v>
       </c>
       <c r="F6" s="10">
-        <v>0</v>
+        <v>135403.32</v>
       </c>
       <c r="G6" s="10">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="H6" s="10">
-        <v>58203</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>38</v>
+        <v>392854</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>42</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" si="0"/>
-        <v>875130.33333333337</v>
+        <v>1171742.68</v>
       </c>
       <c r="K6" s="10">
-        <v>0</v>
+        <v>2232072</v>
       </c>
       <c r="L6" s="10">
-        <v>0</v>
+        <v>1532072</v>
       </c>
       <c r="M6" s="10">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="N6" s="12">
-        <v>0</v>
-      </c>
-      <c r="O6" s="11"/>
+        <v>74059</v>
+      </c>
+      <c r="O6" s="17" t="s">
+        <v>43</v>
+      </c>
       <c r="P6" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>1409013</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>1006116706</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="15">
-        <f>1750905/30*14</f>
+      <c r="C7" s="14">
         <v>817089</v>
       </c>
-      <c r="D7" s="16">
-        <f>249095/30*13</f>
-        <v>107941.16666666666</v>
+      <c r="D7" s="15">
+        <v>116244.33333333333</v>
       </c>
       <c r="E7" s="10">
         <v>0</v>
       </c>
       <c r="F7" s="10">
-        <v>0</v>
+        <v>130734.24</v>
       </c>
       <c r="G7" s="10">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H7" s="10">
-        <f>114922+44700</f>
-        <v>159622</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>39</v>
+        <v>64822</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>44</v>
       </c>
       <c r="J7" s="10">
         <f t="shared" si="0"/>
-        <v>765408.16666666663</v>
+        <v>837777.09333333338</v>
       </c>
       <c r="K7" s="10">
         <v>0</v>
@@ -1076,45 +1110,43 @@
       <c r="N7" s="12">
         <v>0</v>
       </c>
-      <c r="O7" s="11"/>
+      <c r="O7" s="20"/>
       <c r="P7" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="25.5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="27" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>1193092448</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="15">
-        <f>1750905/30*15</f>
+      <c r="C8" s="14">
         <v>875452.5</v>
       </c>
-      <c r="D8" s="16">
-        <f>249095/30*15</f>
+      <c r="D8" s="15">
         <v>124547.49999999999</v>
       </c>
       <c r="E8" s="10">
         <v>0</v>
       </c>
       <c r="F8" s="10">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G8" s="10">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="H8" s="10">
-        <f>197875+35300</f>
-        <v>233175</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>40</v>
+        <v>488388</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>45</v>
       </c>
       <c r="J8" s="10">
         <f t="shared" si="0"/>
-        <v>766825</v>
+        <v>1071539.6000000001</v>
       </c>
       <c r="K8" s="10">
         <v>0</v>
@@ -1128,8 +1160,9 @@
       <c r="N8" s="12">
         <v>0</v>
       </c>
-      <c r="O8" s="11"/>
+      <c r="O8" s="19"/>
       <c r="P8" s="12">
+        <f>L8-M8-N8</f>
         <v>0</v>
       </c>
     </row>
@@ -1140,46 +1173,49 @@
       <c r="B9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="15">
-        <f>1750905/30*15</f>
+      <c r="C9" s="14">
         <v>875452.5</v>
       </c>
-      <c r="D9" s="16">
-        <f>249095/30*15</f>
+      <c r="D9" s="15">
         <v>124547.49999999999</v>
       </c>
       <c r="E9" s="10">
         <v>0</v>
       </c>
       <c r="F9" s="10">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G9" s="10">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="H9" s="10">
-        <v>0</v>
-      </c>
-      <c r="I9" s="14"/>
+        <v>16000</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>46</v>
+      </c>
       <c r="J9" s="10">
         <f t="shared" si="0"/>
-        <v>1000000</v>
+        <v>1143927.6000000001</v>
       </c>
       <c r="K9" s="10">
-        <v>0</v>
+        <v>326404</v>
       </c>
       <c r="L9" s="10">
-        <v>0</v>
+        <v>26404</v>
       </c>
       <c r="M9" s="10">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="N9" s="12">
         <v>0</v>
       </c>
-      <c r="O9" s="11"/>
+      <c r="O9" s="17" t="s">
+        <v>47</v>
+      </c>
       <c r="P9" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>12404</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -1189,32 +1225,30 @@
       <c r="B10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="15">
-        <f>1750905/30*11</f>
-        <v>641998.5</v>
-      </c>
-      <c r="D10" s="16">
-        <f>249095/30*11</f>
-        <v>91334.833333333328</v>
+      <c r="C10" s="14">
+        <v>875452.5</v>
+      </c>
+      <c r="D10" s="15">
+        <v>116244.33333333333</v>
       </c>
       <c r="E10" s="10">
-        <v>23877</v>
+        <v>0</v>
       </c>
       <c r="F10" s="10">
-        <v>0</v>
+        <v>121396.08</v>
       </c>
       <c r="G10" s="10">
         <v>0</v>
       </c>
       <c r="H10" s="10">
-        <v>0</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>41</v>
+        <v>58000</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>48</v>
       </c>
       <c r="J10" s="10">
         <f t="shared" si="0"/>
-        <v>757210.33333333337</v>
+        <v>812300.75333333341</v>
       </c>
       <c r="K10" s="10">
         <v>0</v>
@@ -1228,8 +1262,9 @@
       <c r="N10" s="12">
         <v>0</v>
       </c>
-      <c r="O10" s="11"/>
+      <c r="O10" s="17"/>
       <c r="P10" s="12">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1240,30 +1275,28 @@
       <c r="B11" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="15">
-        <f>+(2150000/30)*15</f>
+      <c r="C11" s="14">
         <v>1075000</v>
       </c>
-      <c r="D11" s="16">
-        <f>249095/30*15</f>
+      <c r="D11" s="15">
         <v>124547.49999999999</v>
       </c>
       <c r="E11" s="10">
         <v>0</v>
       </c>
       <c r="F11" s="10">
-        <v>0</v>
+        <v>172000</v>
       </c>
       <c r="G11" s="10">
-        <v>0</v>
+        <v>850000</v>
       </c>
       <c r="H11" s="10">
         <v>0</v>
       </c>
-      <c r="I11" s="14"/>
+      <c r="I11" s="16"/>
       <c r="J11" s="10">
         <f t="shared" si="0"/>
-        <v>1199547.5</v>
+        <v>1877547.5</v>
       </c>
       <c r="K11" s="10">
         <v>0</v>
@@ -1277,8 +1310,9 @@
       <c r="N11" s="12">
         <v>0</v>
       </c>
-      <c r="O11" s="11"/>
+      <c r="O11" s="20"/>
       <c r="P11" s="12">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1289,34 +1323,34 @@
       <c r="B12" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="14">
         <v>7150000</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="15">
         <v>0</v>
       </c>
       <c r="E12" s="10">
         <v>0</v>
       </c>
       <c r="F12" s="10">
-        <v>0</v>
+        <v>572000</v>
       </c>
       <c r="G12" s="10">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="H12" s="10">
         <v>0</v>
       </c>
-      <c r="I12" s="14"/>
+      <c r="I12" s="16"/>
       <c r="J12" s="10">
         <f t="shared" si="0"/>
-        <v>7150000</v>
+        <v>8578000</v>
       </c>
       <c r="K12" s="10">
         <v>0</v>
       </c>
       <c r="L12" s="10">
-        <v>0</v>
+        <v>572000</v>
       </c>
       <c r="M12" s="10">
         <v>0</v>
@@ -1324,9 +1358,10 @@
       <c r="N12" s="12">
         <v>0</v>
       </c>
-      <c r="O12" s="11"/>
+      <c r="O12" s="20"/>
       <c r="P12" s="12">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>572000</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -1336,32 +1371,30 @@
       <c r="B13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="15">
-        <f>1750905/30*15</f>
-        <v>875452.5</v>
-      </c>
-      <c r="D13" s="16">
-        <f t="shared" ref="D13:D18" si="1">249095/30*15</f>
-        <v>124547.49999999999</v>
+      <c r="C13" s="14">
+        <v>817089</v>
+      </c>
+      <c r="D13" s="15">
+        <v>116244.33333333333</v>
       </c>
       <c r="E13" s="10">
         <v>0</v>
       </c>
       <c r="F13" s="10">
-        <v>0</v>
+        <v>135403.32</v>
       </c>
       <c r="G13" s="10">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H13" s="10">
-        <v>377354</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>42</v>
+        <v>7000</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="J13" s="10">
         <f t="shared" si="0"/>
-        <v>622646</v>
+        <v>890930.01333333342</v>
       </c>
       <c r="K13" s="10">
         <v>0</v>
@@ -1375,8 +1408,9 @@
       <c r="N13" s="12">
         <v>0</v>
       </c>
-      <c r="O13" s="11"/>
+      <c r="O13" s="20"/>
       <c r="P13" s="12">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1387,32 +1421,28 @@
       <c r="B14" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="15">
-        <f>+((2200000/30)*15)</f>
+      <c r="C14" s="14">
         <v>1100000</v>
       </c>
-      <c r="D14" s="16">
-        <f t="shared" si="1"/>
+      <c r="D14" s="15">
         <v>124547.49999999999</v>
       </c>
       <c r="E14" s="10">
         <v>0</v>
       </c>
       <c r="F14" s="10">
-        <v>0</v>
+        <v>176000</v>
       </c>
       <c r="G14" s="10">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="H14" s="10">
-        <v>5000</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>43</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I14" s="20"/>
       <c r="J14" s="10">
         <f t="shared" si="0"/>
-        <v>1219547.5</v>
+        <v>1648547.5</v>
       </c>
       <c r="K14" s="10">
         <v>0</v>
@@ -1426,8 +1456,9 @@
       <c r="N14" s="12">
         <v>0</v>
       </c>
-      <c r="O14" s="11"/>
+      <c r="O14" s="20"/>
       <c r="P14" s="12">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1438,32 +1469,30 @@
       <c r="B15" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="15">
-        <f t="shared" ref="C15:C20" si="2">1750905/30*15</f>
+      <c r="C15" s="14">
         <v>875452.5</v>
       </c>
-      <c r="D15" s="16">
-        <f t="shared" si="1"/>
+      <c r="D15" s="15">
         <v>124547.49999999999</v>
       </c>
       <c r="E15" s="10">
         <v>0</v>
       </c>
       <c r="F15" s="10">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G15" s="10">
         <v>0</v>
       </c>
       <c r="H15" s="10">
-        <v>163300</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>44</v>
+        <v>35000</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>50</v>
       </c>
       <c r="J15" s="10">
         <f t="shared" si="0"/>
-        <v>836700</v>
+        <v>824927.6</v>
       </c>
       <c r="K15" s="10">
         <v>0</v>
@@ -1477,8 +1506,9 @@
       <c r="N15" s="12">
         <v>0</v>
       </c>
-      <c r="O15" s="11"/>
+      <c r="O15" s="20"/>
       <c r="P15" s="12">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1489,32 +1519,30 @@
       <c r="B16" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="15">
-        <f t="shared" si="2"/>
+      <c r="C16" s="14">
         <v>875452.5</v>
       </c>
-      <c r="D16" s="16">
-        <f t="shared" si="1"/>
+      <c r="D16" s="15">
         <v>124547.49999999999</v>
       </c>
       <c r="E16" s="10">
-        <v>0</v>
+        <v>396543</v>
       </c>
       <c r="F16" s="10">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G16" s="10">
         <v>0</v>
       </c>
       <c r="H16" s="10">
-        <v>25000</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>45</v>
+        <v>28000</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>51</v>
       </c>
       <c r="J16" s="10">
         <f t="shared" si="0"/>
-        <v>975000</v>
+        <v>1228470.6000000001</v>
       </c>
       <c r="K16" s="10">
         <v>0</v>
@@ -1528,8 +1556,9 @@
       <c r="N16" s="12">
         <v>0</v>
       </c>
-      <c r="O16" s="11"/>
+      <c r="O16" s="20"/>
       <c r="P16" s="12">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1540,32 +1569,30 @@
       <c r="B17" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="15">
-        <f t="shared" si="2"/>
-        <v>875452.5</v>
-      </c>
-      <c r="D17" s="16">
-        <f t="shared" si="1"/>
-        <v>124547.49999999999</v>
+      <c r="C17" s="14">
+        <v>817089</v>
+      </c>
+      <c r="D17" s="15">
+        <v>116244.33333333333</v>
       </c>
       <c r="E17" s="10">
-        <v>0</v>
+        <v>337121</v>
       </c>
       <c r="F17" s="10">
-        <v>0</v>
+        <v>135403.32</v>
       </c>
       <c r="G17" s="10">
         <v>0</v>
       </c>
       <c r="H17" s="10">
-        <v>210000</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>46</v>
+        <v>291147</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="J17" s="10">
         <f t="shared" si="0"/>
-        <v>790000</v>
+        <v>843904.01333333342</v>
       </c>
       <c r="K17" s="10">
         <v>0</v>
@@ -1579,8 +1606,9 @@
       <c r="N17" s="12">
         <v>0</v>
       </c>
-      <c r="O17" s="11"/>
+      <c r="O17" s="20"/>
       <c r="P17" s="12">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1591,32 +1619,30 @@
       <c r="B18" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="15">
-        <f t="shared" si="2"/>
-        <v>875452.5</v>
-      </c>
-      <c r="D18" s="16">
-        <f t="shared" si="1"/>
-        <v>124547.49999999999</v>
+      <c r="C18" s="14">
+        <v>817089</v>
+      </c>
+      <c r="D18" s="15">
+        <v>116244.33333333333</v>
       </c>
       <c r="E18" s="10">
         <v>0</v>
       </c>
       <c r="F18" s="10">
-        <v>0</v>
+        <v>135403.32</v>
       </c>
       <c r="G18" s="10">
         <v>0</v>
       </c>
       <c r="H18" s="10">
-        <v>80000</v>
-      </c>
-      <c r="I18" s="14" t="s">
-        <v>47</v>
+        <v>112992</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>53</v>
       </c>
       <c r="J18" s="10">
         <f t="shared" si="0"/>
-        <v>920000</v>
+        <v>684938.01333333342</v>
       </c>
       <c r="K18" s="10">
         <v>0</v>
@@ -1630,8 +1656,9 @@
       <c r="N18" s="12">
         <v>0</v>
       </c>
-      <c r="O18" s="11"/>
+      <c r="O18" s="20"/>
       <c r="P18" s="12">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1642,32 +1669,30 @@
       <c r="B19" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="15">
-        <f t="shared" si="2"/>
+      <c r="C19" s="14">
         <v>875452.5</v>
       </c>
-      <c r="D19" s="16">
-        <f>249095/30*14</f>
+      <c r="D19" s="15">
         <v>116244.33333333333</v>
       </c>
       <c r="E19" s="10">
-        <v>0</v>
+        <v>308031</v>
       </c>
       <c r="F19" s="10">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G19" s="10">
         <v>0</v>
       </c>
       <c r="H19" s="10">
-        <v>155000</v>
-      </c>
-      <c r="I19" s="14" t="s">
-        <v>48</v>
+        <v>0</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>54</v>
       </c>
       <c r="J19" s="10">
         <f t="shared" si="0"/>
-        <v>836696.83333333337</v>
+        <v>1159655.4333333336</v>
       </c>
       <c r="K19" s="10">
         <v>0</v>
@@ -1681,8 +1706,9 @@
       <c r="N19" s="12">
         <v>0</v>
       </c>
-      <c r="O19" s="11"/>
+      <c r="O19" s="20"/>
       <c r="P19" s="12">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1693,30 +1719,30 @@
       <c r="B20" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="15">
-        <f t="shared" si="2"/>
+      <c r="C20" s="14">
         <v>875452.5</v>
       </c>
-      <c r="D20" s="16">
-        <f>249095/30*15</f>
-        <v>124547.49999999999</v>
+      <c r="D20" s="15">
+        <v>116244.33333333333</v>
       </c>
       <c r="E20" s="10">
-        <v>0</v>
+        <v>361288</v>
       </c>
       <c r="F20" s="10">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G20" s="10">
         <v>0</v>
       </c>
       <c r="H20" s="10">
-        <v>0</v>
-      </c>
-      <c r="I20" s="17"/>
+        <v>151729</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>55</v>
+      </c>
       <c r="J20" s="10">
         <f>+C20+D20+E20-F20+G20-H20</f>
-        <v>1000000</v>
+        <v>1061183.4333333336</v>
       </c>
       <c r="K20" s="10">
         <v>0</v>
@@ -1730,22 +1756,44 @@
       <c r="N20" s="12">
         <v>0</v>
       </c>
-      <c r="O20" s="11"/>
+      <c r="O20" s="20"/>
       <c r="P20" s="12">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="10"/>
+      <c r="A21" s="6">
+        <v>1013673759</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="14">
+        <v>466908</v>
+      </c>
+      <c r="D21" s="15">
+        <v>66425.333333333328</v>
+      </c>
+      <c r="E21" s="10">
+        <v>0</v>
+      </c>
+      <c r="F21" s="10">
+        <v>37352.639999999999</v>
+      </c>
+      <c r="G21" s="10">
+        <v>0</v>
+      </c>
+      <c r="H21" s="10">
+        <v>150000</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="J21" s="10">
+        <f>+C21+D21+E21-F21+G21-H21</f>
+        <v>345980.69333333336</v>
+      </c>
       <c r="K21" s="10">
         <v>0</v>
       </c>
@@ -1758,10 +1806,28 @@
       <c r="N21" s="12">
         <v>0</v>
       </c>
-      <c r="O21" s="11"/>
+      <c r="O21" s="20"/>
       <c r="P21" s="12">
         <v>0</v>
       </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
